--- a/WB_nalog_USN_NDS.xlsx
+++ b/WB_nalog_USN_NDS.xlsx
@@ -108,12 +108,6 @@
     <t>Отчетов По выкупам</t>
   </si>
   <si>
-    <t>Ставка НДС до лимита ,%</t>
-  </si>
-  <si>
-    <t>Ставка НДС после лимита ,%</t>
-  </si>
-  <si>
     <t>Сумма дохода за прошлый год ,р.</t>
   </si>
   <si>
@@ -124,6 +118,12 @@
   </si>
   <si>
     <t>Ставка налога по УСН ,%</t>
+  </si>
+  <si>
+    <t>Ставка НДС до превышения порога ,%</t>
+  </si>
+  <si>
+    <t>Ставка НДС после превышения порога ,%</t>
   </si>
 </sst>
 </file>
@@ -783,7 +783,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7"/>
     </row>
@@ -862,7 +862,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B3" s="13">
         <v>0</v>
@@ -870,7 +870,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" s="15">
         <v>0.05</v>
@@ -878,7 +878,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="16">
         <v>20000000</v>
@@ -886,7 +886,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B6" s="17">
         <v>60000000</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" s="17">
         <v>20000000</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="18">
         <v>0.01</v>

--- a/WB_nalog_USN_NDS.xlsx
+++ b/WB_nalog_USN_NDS.xlsx
@@ -5,24 +5,25 @@
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Игорь\Проекты\Расчет налогов\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\AOTC\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25860" windowHeight="14385" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25860" windowHeight="14385" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
     <sheet name="Свод" sheetId="2" r:id="rId2"/>
     <sheet name="Контроль" sheetId="3" r:id="rId3"/>
     <sheet name="Настройки" sheetId="4" r:id="rId4"/>
+    <sheet name="Календарь" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
   <si>
     <t>Месяц</t>
   </si>
@@ -111,28 +112,180 @@
     <t>Сумма дохода за прошлый год ,р.</t>
   </si>
   <si>
-    <t>Порог дохода за прошлый год (НДС) ,р</t>
-  </si>
-  <si>
-    <t>Порог дохода за текущий год (НДС) ,р</t>
-  </si>
-  <si>
     <t>Ставка налога по УСН ,%</t>
   </si>
   <si>
-    <t>Ставка НДС до превышения порога ,%</t>
-  </si>
-  <si>
-    <t>Ставка НДС после превышения порога ,%</t>
+    <t>Мероприятие</t>
+  </si>
+  <si>
+    <t>Плановый срок</t>
+  </si>
+  <si>
+    <t>Оплата фиксированных страховых взносов за 2025</t>
+  </si>
+  <si>
+    <t>Подача декларации НДС за 4 кв 2025</t>
+  </si>
+  <si>
+    <t>Оплата НДС 1/3 за 4 кв 2025</t>
+  </si>
+  <si>
+    <t>Оплата НДС 2/3 за 4 кв 2025</t>
+  </si>
+  <si>
+    <t>Оплата НДС 3/3 за 4 кв 2025</t>
+  </si>
+  <si>
+    <t>Оплата экологического сбора</t>
+  </si>
+  <si>
+    <t>Подача декларации УСН за 2025</t>
+  </si>
+  <si>
+    <t>Оплата налога УСН за 2025</t>
+  </si>
+  <si>
+    <t>Оплата НДС 1/3 за 1 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата НДС 2/3 за 1 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата НДС 3/3 за 1 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата аванса УСН полугодие</t>
+  </si>
+  <si>
+    <t>Оплата дополнительного страхового взноса 1%</t>
+  </si>
+  <si>
+    <t>Подача декларации НДС за 2 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата НДС 1/3 за 2 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата НДС 2/3 за 2 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата НДС 3/3 за 2 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата аванса УСН 9 месяцев</t>
+  </si>
+  <si>
+    <t>Подача декларации НДС за 3 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата НДС 1/3 за 3 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата НДС 2/3 за 3 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата НДС 3/3 за 3 кв 2026</t>
+  </si>
+  <si>
+    <t>Оплата фиксированных страховых взносов за 2026</t>
+  </si>
+  <si>
+    <t>Оплата аванса УСН 1 квартал</t>
+  </si>
+  <si>
+    <t>Подача отчетности РПН</t>
+  </si>
+  <si>
+    <t>Подача декларации НДС за 1 кв 2026</t>
+  </si>
+  <si>
+    <t>Примечание</t>
+  </si>
+  <si>
+    <t>Ставка НДС до лимита ,%</t>
+  </si>
+  <si>
+    <t>Ставка НДС после лимита ,%</t>
+  </si>
+  <si>
+    <t>Порог дохода за прошлый год (НДС) ,р.</t>
+  </si>
+  <si>
+    <t>Порог дохода за текущий год (НДС) ,р.</t>
+  </si>
+  <si>
+    <t>Январь</t>
+  </si>
+  <si>
+    <t>Февраль</t>
+  </si>
+  <si>
+    <t>Март</t>
+  </si>
+  <si>
+    <t>Апрель</t>
+  </si>
+  <si>
+    <t>Май</t>
+  </si>
+  <si>
+    <t>Июнь</t>
+  </si>
+  <si>
+    <t>Июль</t>
+  </si>
+  <si>
+    <t>Август</t>
+  </si>
+  <si>
+    <t>Сентябрь</t>
+  </si>
+  <si>
+    <t>Октябрь</t>
+  </si>
+  <si>
+    <t>Ноябрь</t>
+  </si>
+  <si>
+    <t>Декабрь</t>
+  </si>
+  <si>
+    <t>Итого за 1 квартал</t>
+  </si>
+  <si>
+    <t>Итого за 2 квартал</t>
+  </si>
+  <si>
+    <t>Итого за 3 квартал</t>
+  </si>
+  <si>
+    <t>Итого за 4 квартал</t>
+  </si>
+  <si>
+    <t>Итого за год</t>
+  </si>
+  <si>
+    <t>Сумма, р.</t>
+  </si>
+  <si>
+    <t>Кап 1% взноса ,р.</t>
+  </si>
+  <si>
+    <t>Сумма фиксированных страховых взносов за 2025 ,р.</t>
+  </si>
+  <si>
+    <t>Сумма дополнительного страхового взноса за 2025 ,р.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0\ &quot;₽&quot;"/>
+    <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -212,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -246,6 +399,12 @@
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -676,7 +835,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:L31">
+  <sortState ref="A2:M31">
     <sortCondition ref="B2:B31"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -687,7 +846,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -722,7 +881,7 @@
         <v>21</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>25</v>
@@ -735,16 +894,93 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
       <c r="H4" s="3"/>
     </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+    </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
       <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -770,22 +1006,22 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="23"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="23"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="7"/>
+      <c r="A4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="23"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -837,10 +1073,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист4"/>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.85546875" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -862,7 +1098,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B3" s="13">
         <v>0</v>
@@ -870,7 +1106,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B4" s="15">
         <v>0.05</v>
@@ -881,12 +1117,12 @@
         <v>28</v>
       </c>
       <c r="B5" s="16">
-        <v>20000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="B6" s="17">
         <v>60000000</v>
@@ -894,7 +1130,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="B7" s="17">
         <v>20000000</v>
@@ -902,10 +1138,34 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="18">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="17">
+        <v>277571</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="24">
+        <v>141514.24650000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="16">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -942,4 +1202,320 @@
     </mc:Choice>
   </mc:AlternateContent>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист5"/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="20">
+        <v>46031</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="20">
+        <v>46047</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="20">
+        <v>46050</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="20">
+        <v>46081</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="20">
+        <v>46109</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="20">
+        <v>46113</v>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="20">
+        <v>46127</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="20">
+        <v>46137</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="20">
+        <v>46140</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="20">
+        <v>46140</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="20">
+        <v>46142</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="20">
+        <v>46142</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="20">
+        <v>46170</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="20">
+        <v>46201</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="20">
+        <v>46204</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="20">
+        <v>46228</v>
+      </c>
+      <c r="C17" s="21">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="20">
+        <v>46231</v>
+      </c>
+      <c r="C18" s="21">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="20">
+        <v>46231</v>
+      </c>
+      <c r="C19" s="21">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="20">
+        <v>46262</v>
+      </c>
+      <c r="C20" s="21">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="20">
+        <v>46293</v>
+      </c>
+      <c r="C21" s="21">
+        <v>0</v>
+      </c>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="20">
+        <v>46320</v>
+      </c>
+      <c r="C22" s="21">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="20">
+        <v>46323</v>
+      </c>
+      <c r="C23" s="21">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="20">
+        <v>46323</v>
+      </c>
+      <c r="C24" s="21">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="20">
+        <v>46354</v>
+      </c>
+      <c r="C25" s="21">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="20">
+        <v>46384</v>
+      </c>
+      <c r="C26" s="21">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="20">
+        <v>46387</v>
+      </c>
+      <c r="C27" s="21">
+        <v>0</v>
+      </c>
+      <c r="D27" s="7"/>
+    </row>
+  </sheetData>
+  <sortState ref="A2:C27">
+    <sortCondition ref="B1"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/WB_nalog_USN_NDS.xlsx
+++ b/WB_nalog_USN_NDS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25860" windowHeight="14385" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25860" windowHeight="14385"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
   <si>
     <t>Месяц</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Доход без НДС ,р.</t>
   </si>
   <si>
-    <t>Доход без НДС ,р.)</t>
-  </si>
-  <si>
     <t>Ставка НДС, %</t>
   </si>
   <si>
@@ -214,57 +211,6 @@
     <t>Порог дохода за текущий год (НДС) ,р.</t>
   </si>
   <si>
-    <t>Январь</t>
-  </si>
-  <si>
-    <t>Февраль</t>
-  </si>
-  <si>
-    <t>Март</t>
-  </si>
-  <si>
-    <t>Апрель</t>
-  </si>
-  <si>
-    <t>Май</t>
-  </si>
-  <si>
-    <t>Июнь</t>
-  </si>
-  <si>
-    <t>Июль</t>
-  </si>
-  <si>
-    <t>Август</t>
-  </si>
-  <si>
-    <t>Сентябрь</t>
-  </si>
-  <si>
-    <t>Октябрь</t>
-  </si>
-  <si>
-    <t>Ноябрь</t>
-  </si>
-  <si>
-    <t>Декабрь</t>
-  </si>
-  <si>
-    <t>Итого за 1 квартал</t>
-  </si>
-  <si>
-    <t>Итого за 2 квартал</t>
-  </si>
-  <si>
-    <t>Итого за 3 квартал</t>
-  </si>
-  <si>
-    <t>Итого за 4 квартал</t>
-  </si>
-  <si>
-    <t>Итого за год</t>
-  </si>
-  <si>
     <t>Сумма, р.</t>
   </si>
   <si>
@@ -275,6 +221,15 @@
   </si>
   <si>
     <t>Сумма дополнительного страхового взноса за 2025 ,р.</t>
+  </si>
+  <si>
+    <t>Доход с НДС накптиельным итогом ,р.</t>
+  </si>
+  <si>
+    <t>Сумма НДС накптиельным итогом ,р.</t>
+  </si>
+  <si>
+    <t>Доход без НДС накптиельным итогом ,р.)</t>
   </si>
 </sst>
 </file>
@@ -846,7 +801,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -884,103 +839,26 @@
         <v>23</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-    </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>66</v>
-      </c>
       <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>79</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1007,19 +885,19 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="B2" s="23"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="B3" s="23"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B4" s="23"/>
     </row>
@@ -1098,7 +976,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="13">
         <v>0</v>
@@ -1106,7 +984,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="15">
         <v>0.05</v>
@@ -1114,7 +992,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="16">
         <v>0</v>
@@ -1122,7 +1000,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="17">
         <v>60000000</v>
@@ -1130,7 +1008,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B7" s="17">
         <v>20000000</v>
@@ -1138,15 +1016,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="18">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B9" s="17">
         <v>277571</v>
@@ -1154,15 +1032,15 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B10" s="24">
-        <v>141514.24650000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B11" s="16">
         <v>0</v>
@@ -1218,21 +1096,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>31</v>
-      </c>
       <c r="C1" s="21" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="20">
         <v>46031</v>
@@ -1242,7 +1120,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="20">
         <v>46047</v>
@@ -1252,7 +1130,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="20">
         <v>46050</v>
@@ -1262,7 +1140,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="20">
         <v>46081</v>
@@ -1272,7 +1150,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="20">
         <v>46109</v>
@@ -1282,17 +1160,17 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" s="20">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="C7" s="21"/>
       <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" s="20">
         <v>46127</v>
@@ -1302,7 +1180,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="20">
         <v>46137</v>
@@ -1312,7 +1190,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" s="20">
         <v>46140</v>
@@ -1322,7 +1200,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="20">
         <v>46140</v>
@@ -1332,27 +1210,27 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="20">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="20">
-        <v>46142</v>
+        <v>46140</v>
       </c>
       <c r="C13" s="21"/>
       <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="20">
         <v>46170</v>
@@ -1362,7 +1240,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="20">
         <v>46201</v>
@@ -1372,7 +1250,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="20">
         <v>46204</v>
@@ -1382,134 +1260,112 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="20">
         <v>46228</v>
       </c>
-      <c r="C17" s="21">
-        <v>0</v>
-      </c>
+      <c r="C17" s="21"/>
       <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="20">
         <v>46231</v>
       </c>
-      <c r="C18" s="21">
-        <v>0</v>
-      </c>
+      <c r="C18" s="21"/>
       <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="20">
         <v>46231</v>
       </c>
-      <c r="C19" s="21">
-        <v>0</v>
-      </c>
+      <c r="C19" s="21"/>
       <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" s="20">
         <v>46262</v>
       </c>
-      <c r="C20" s="21">
-        <v>0</v>
-      </c>
+      <c r="C20" s="21"/>
       <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="20">
         <v>46293</v>
       </c>
-      <c r="C21" s="21">
-        <v>0</v>
-      </c>
+      <c r="C21" s="21"/>
       <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22" s="20">
         <v>46320</v>
       </c>
-      <c r="C22" s="21">
-        <v>0</v>
-      </c>
+      <c r="C22" s="21"/>
       <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="20">
         <v>46323</v>
       </c>
-      <c r="C23" s="21">
-        <v>0</v>
-      </c>
+      <c r="C23" s="21"/>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="20">
         <v>46323</v>
       </c>
-      <c r="C24" s="21">
-        <v>0</v>
-      </c>
+      <c r="C24" s="21"/>
       <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="20">
         <v>46354</v>
       </c>
-      <c r="C25" s="21">
-        <v>0</v>
-      </c>
+      <c r="C25" s="21"/>
       <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" s="20">
         <v>46384</v>
       </c>
-      <c r="C26" s="21">
-        <v>0</v>
-      </c>
+      <c r="C26" s="21"/>
       <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B27" s="20">
         <v>46387</v>
       </c>
-      <c r="C27" s="21">
-        <v>0</v>
-      </c>
+      <c r="C27" s="21"/>
       <c r="D27" s="7"/>
     </row>
   </sheetData>

--- a/WB_nalog_USN_NDS.xlsx
+++ b/WB_nalog_USN_NDS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25860" windowHeight="14385"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25860" windowHeight="14385" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>Номер отчёта</t>
   </si>
   <si>
-    <t>F:\Отчеты по реализации</t>
-  </si>
-  <si>
     <t>Дата превышения порога</t>
   </si>
   <si>
@@ -230,6 +227,9 @@
   </si>
   <si>
     <t>Доход без НДС накптиельным итогом ,р.)</t>
+  </si>
+  <si>
+    <t>F:\Отчеты по реализации\2025</t>
   </si>
 </sst>
 </file>
@@ -756,31 +756,31 @@
   <sheetData>
     <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>16</v>
-      </c>
       <c r="D1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>4</v>
@@ -790,8 +790,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:M31">
-    <sortCondition ref="B2:B31"/>
+  <sortState ref="A2:M25">
+    <sortCondition ref="B2:B25"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -801,7 +801,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -821,44 +821,41 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H4" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H6" s="3"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -885,37 +882,37 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" s="23"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="23"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="23"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="8"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="8"/>
     </row>
@@ -968,15 +965,15 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="13">
         <v>0</v>
@@ -984,7 +981,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="15">
         <v>0.05</v>
@@ -992,7 +989,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="16">
         <v>0</v>
@@ -1000,7 +997,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="17">
         <v>60000000</v>
@@ -1008,7 +1005,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="17">
         <v>20000000</v>
@@ -1016,7 +1013,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="18">
         <v>0.06</v>
@@ -1024,7 +1021,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="17">
         <v>277571</v>
@@ -1032,7 +1029,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="24">
         <v>0</v>
@@ -1040,7 +1037,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="16">
         <v>0</v>
@@ -1090,27 +1087,27 @@
   <cols>
     <col min="1" max="1" width="47.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>30</v>
-      </c>
       <c r="C1" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="20">
         <v>46031</v>
@@ -1120,7 +1117,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="20">
         <v>46047</v>
@@ -1130,7 +1127,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="20">
         <v>46050</v>
@@ -1140,7 +1137,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="20">
         <v>46081</v>
@@ -1150,7 +1147,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="20">
         <v>46109</v>
@@ -1160,7 +1157,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="20">
         <v>46126</v>
@@ -1170,7 +1167,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="20">
         <v>46127</v>
@@ -1180,7 +1177,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" s="20">
         <v>46137</v>
@@ -1190,7 +1187,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="20">
         <v>46140</v>
@@ -1200,7 +1197,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="20">
         <v>46140</v>
@@ -1210,7 +1207,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="20">
         <v>46139</v>
@@ -1220,7 +1217,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="20">
         <v>46140</v>
@@ -1230,7 +1227,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="20">
         <v>46170</v>
@@ -1240,7 +1237,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="20">
         <v>46201</v>
@@ -1250,7 +1247,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="20">
         <v>46204</v>
@@ -1260,7 +1257,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="20">
         <v>46228</v>
@@ -1270,7 +1267,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="20">
         <v>46231</v>
@@ -1280,7 +1277,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B19" s="20">
         <v>46231</v>
@@ -1290,7 +1287,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="20">
         <v>46262</v>
@@ -1300,7 +1297,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" s="20">
         <v>46293</v>
@@ -1310,7 +1307,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="20">
         <v>46320</v>
@@ -1320,7 +1317,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B23" s="20">
         <v>46323</v>
@@ -1330,7 +1327,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24" s="20">
         <v>46323</v>
@@ -1340,7 +1337,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="20">
         <v>46354</v>
@@ -1350,7 +1347,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="20">
         <v>46384</v>
@@ -1360,7 +1357,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" s="20">
         <v>46387</v>
